--- a/daily_matches/job_matches_2026-07-12.xlsx
+++ b/daily_matches/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Software Engineer - X Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Xai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, BigQuery, Git, Databricks, BigQuery, PySpark</t>
+          <t>RAG, BigQuery, BigQuery, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=95e4437e4a378bd5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Kinesis, CI/CD, Git, Databricks, Kafka, Cassandra, NoSQL, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=faa1ca9a4146699c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Clinical AI</t>
+          <t>Data Scientist 2 - Virtual - Freewheel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, BigQuery, CI/CD, BigQuery</t>
+          <t>Data Scientist, Generative AI, Git, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,147 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6200ddf87a72813a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9be1cfabf127f765</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ross Dress For Less</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ross Dress For Less</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Snowflake, Power BI, MicroStrategy, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2a63ca85405a60</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Zions Bancorporation</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Midvale, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf00e04af81304c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ee72add7642b1b8</t>
         </is>
       </c>
     </row>
